--- a/super-admin-paneli/Ornek_Exceller/Siniflar_Ornek.xlsx
+++ b/super-admin-paneli/Ornek_Exceller/Siniflar_Ornek.xlsx
@@ -397,17 +397,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Oda_Kodu</v>
+        <v>oda_kodu</v>
       </c>
       <c r="B1" t="str">
-        <v>Kapasite</v>
+        <v>kapasite</v>
       </c>
       <c r="C1" t="str">
-        <v>Tur</v>
+        <v>tur</v>
       </c>
     </row>
     <row r="2">
@@ -423,29 +423,73 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LAB-1</v>
+        <v>A-102</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C3" t="str">
-        <v>lab</v>
+        <v>theory</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>B-202</v>
+        <v>A-201</v>
       </c>
       <c r="B4">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C4" t="str">
         <v>theory</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>B-101</v>
+      </c>
+      <c r="B5">
+        <v>35</v>
+      </c>
+      <c r="C5" t="str">
+        <v>theory</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LAB-1</v>
+      </c>
+      <c r="B6">
+        <v>25</v>
+      </c>
+      <c r="C6" t="str">
+        <v>lab</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LAB-2</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7" t="str">
+        <v>lab</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LAB-3</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
+      </c>
+      <c r="C8" t="str">
+        <v>lab</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
   </ignoredErrors>
 </worksheet>
 </file>